--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="33">
   <si>
     <t>Docente</t>
   </si>
@@ -87,28 +87,13 @@
     <t>6AEM</t>
   </si>
   <si>
-    <t>6ALCM</t>
-  </si>
-  <si>
     <t>6APM</t>
   </si>
   <si>
-    <t>6ARHM</t>
-  </si>
-  <si>
     <t>6BEM</t>
   </si>
   <si>
-    <t>6BLCM</t>
-  </si>
-  <si>
     <t>6AEV</t>
-  </si>
-  <si>
-    <t>6ALCV</t>
-  </si>
-  <si>
-    <t>6ARHV</t>
   </si>
   <si>
     <t>6APV</t>
@@ -493,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -546,28 +531,31 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -578,7 +566,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -610,28 +598,31 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -642,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -674,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -706,28 +697,31 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -738,7 +732,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -770,7 +764,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -802,7 +796,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>30</v>
@@ -837,18 +831,30 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G11" s="1">
+        <v>35</v>
+      </c>
+      <c r="H11" s="1">
+        <v>65</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -860,25 +866,25 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>35</v>
+        <v>32.14</v>
       </c>
       <c r="H12" s="1">
-        <v>65</v>
+        <v>67.86</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -895,48 +901,60 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G13" s="1">
+        <v>42.86</v>
+      </c>
+      <c r="H13" s="1">
+        <v>57.14</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5.1</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>32.14</v>
+        <v>41.18</v>
       </c>
       <c r="H14" s="1">
-        <v>67.86</v>
+        <v>58.82</v>
       </c>
       <c r="I14" s="2">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -947,277 +965,138 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G15" s="1">
+        <v>57.89</v>
+      </c>
+      <c r="H15" s="1">
+        <v>42.11</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5.9</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>57.14</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>54.17</v>
+      </c>
+      <c r="H17" s="1">
+        <v>45.83</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>14.29</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>7</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1">
-        <v>41.18</v>
-      </c>
-      <c r="H19" s="1">
-        <v>58.82</v>
-      </c>
-      <c r="I19" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20">
-        <v>19</v>
-      </c>
-      <c r="E20">
-        <v>11</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="G20" s="1">
-        <v>57.89</v>
-      </c>
-      <c r="H20" s="1">
-        <v>42.11</v>
-      </c>
-      <c r="I20" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>33</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>100</v>
-      </c>
-      <c r="J21">
-        <v>33</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>13</v>
-      </c>
-      <c r="F22">
-        <v>11</v>
-      </c>
-      <c r="G22" s="1">
-        <v>54.17</v>
-      </c>
-      <c r="H22" s="1">
-        <v>45.83</v>
-      </c>
-      <c r="I22" s="2">
-        <v>6</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23">
-        <v>14</v>
-      </c>
-      <c r="E23">
-        <v>12</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H23" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I23" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1228,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1281,7 +1160,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>31</v>
@@ -1313,7 +1192,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -1345,7 +1224,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>27</v>
@@ -1377,7 +1256,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -1409,7 +1288,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -1441,7 +1320,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>41</v>
@@ -1473,7 +1352,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -1505,7 +1384,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -1537,7 +1416,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>30</v>
@@ -1569,19 +1448,28 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1592,16 +1480,16 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1610,7 +1498,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1624,39 +1512,48 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1665,7 +1562,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1673,45 +1570,54 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1720,7 +1626,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1728,207 +1634,65 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>17</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>100</v>
-      </c>
-      <c r="J19">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20">
-        <v>19</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>19</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>19</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>33</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>100</v>
-      </c>
-      <c r="J21">
-        <v>33</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>24</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>100</v>
-      </c>
-      <c r="J22">
-        <v>24</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23">
         <v>14</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>14</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>14</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="K18" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1939,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1992,28 +1756,31 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2024,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>41</v>
@@ -2056,28 +1823,31 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2088,7 +1858,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>38</v>
@@ -2120,7 +1890,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>28</v>
@@ -2152,28 +1922,31 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2184,7 +1957,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -2216,7 +1989,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>29</v>
@@ -2248,7 +2021,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>30</v>
@@ -2283,18 +2056,30 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G11" s="1">
+        <v>35</v>
+      </c>
+      <c r="H11" s="1">
+        <v>65</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2306,25 +2091,25 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>35</v>
+        <v>32.14</v>
       </c>
       <c r="H12" s="1">
-        <v>65</v>
+        <v>67.86</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2341,48 +2126,60 @@
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G13" s="1">
+        <v>42.86</v>
+      </c>
+      <c r="H13" s="1">
+        <v>57.14</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5.5</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>32.14</v>
+        <v>41.18</v>
       </c>
       <c r="H14" s="1">
-        <v>67.86</v>
+        <v>58.82</v>
       </c>
       <c r="I14" s="2">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2393,277 +2190,138 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G15" s="1">
+        <v>57.89</v>
+      </c>
+      <c r="H15" s="1">
+        <v>42.11</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.2</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G16" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>57.14</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5.5</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>54.17</v>
+      </c>
+      <c r="H17" s="1">
+        <v>45.83</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H18" s="1">
+        <v>14.29</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19">
-        <v>17</v>
-      </c>
-      <c r="E19">
-        <v>7</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-      <c r="G19" s="1">
-        <v>41.18</v>
-      </c>
-      <c r="H19" s="1">
-        <v>58.82</v>
-      </c>
-      <c r="I19" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20">
-        <v>19</v>
-      </c>
-      <c r="E20">
-        <v>11</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="G20" s="1">
-        <v>57.89</v>
-      </c>
-      <c r="H20" s="1">
-        <v>42.11</v>
-      </c>
-      <c r="I20" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>33</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>100</v>
-      </c>
-      <c r="J21">
-        <v>33</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22">
-        <v>24</v>
-      </c>
-      <c r="E22">
-        <v>13</v>
-      </c>
-      <c r="F22">
-        <v>11</v>
-      </c>
-      <c r="G22" s="1">
-        <v>54.17</v>
-      </c>
-      <c r="H22" s="1">
-        <v>45.83</v>
-      </c>
-      <c r="I22" s="2">
-        <v>6</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23">
-        <v>14</v>
-      </c>
-      <c r="E23">
-        <v>12</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H23" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I23" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -572,22 +572,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>9.76</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -639,22 +642,25 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -738,22 +744,25 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.3</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -770,22 +779,25 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>3.45</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.1</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1012,22 +1024,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>39.39</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5.9</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1797,22 +1812,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>9.76</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1864,22 +1882,25 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1963,22 +1984,25 @@
         <v>32</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.3</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1995,22 +2019,25 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>96.55</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>3.45</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.1</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2237,22 +2264,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>39.39</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5.9</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -677,22 +677,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>21.43</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.1</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1917,22 +1920,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>21.43</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -779,28 +779,28 @@
         <v>31</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>28</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H9" s="1">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="I9" s="2">
         <v>6.1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1024,28 +1024,28 @@
         <v>31</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>20</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H16" s="1">
-        <v>39.39</v>
+        <v>41.18</v>
       </c>
       <c r="I16" s="2">
         <v>5.9</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1405,13 +1405,13 @@
         <v>31</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1629,13 +1629,13 @@
         <v>31</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2022,28 +2022,28 @@
         <v>31</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>28</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="H9" s="1">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
       <c r="I9" s="2">
         <v>6.1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2267,28 +2267,28 @@
         <v>31</v>
       </c>
       <c r="D16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16">
         <v>20</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>60.61</v>
+        <v>58.82</v>
       </c>
       <c r="H16" s="1">
-        <v>39.39</v>
+        <v>41.18</v>
       </c>
       <c r="I16" s="2">
         <v>5.9</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17" spans="1:11">

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="34">
   <si>
     <t>Docente</t>
   </si>
@@ -51,57 +51,60 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>6AEM</t>
+  </si>
+  <si>
+    <t>6APM</t>
+  </si>
+  <si>
+    <t>6BEM</t>
+  </si>
+  <si>
+    <t>6AEV</t>
+  </si>
+  <si>
+    <t>6APV</t>
+  </si>
+  <si>
+    <t>6ASV</t>
+  </si>
+  <si>
+    <t>4ALCM</t>
+  </si>
+  <si>
+    <t>4ARHM</t>
+  </si>
+  <si>
+    <t>4BEM</t>
+  </si>
+  <si>
+    <t>4AEV</t>
+  </si>
+  <si>
+    <t>4ARHV</t>
+  </si>
+  <si>
     <t>4AEM</t>
   </si>
   <si>
-    <t>4ALCM</t>
-  </si>
-  <si>
     <t>4APM</t>
   </si>
   <si>
-    <t>4ARHM</t>
-  </si>
-  <si>
-    <t>4BEM</t>
-  </si>
-  <si>
     <t>4BLCM</t>
   </si>
   <si>
-    <t>4AEV</t>
-  </si>
-  <si>
-    <t>4ARHV</t>
-  </si>
-  <si>
-    <t>6AEM</t>
-  </si>
-  <si>
-    <t>6APM</t>
-  </si>
-  <si>
-    <t>6BEM</t>
-  </si>
-  <si>
-    <t>6AEV</t>
-  </si>
-  <si>
-    <t>6APV</t>
-  </si>
-  <si>
-    <t>6ASV</t>
-  </si>
-  <si>
     <t>4ALCV</t>
   </si>
   <si>
@@ -111,10 +114,10 @@
     <t>4ASV</t>
   </si>
   <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
     <t>FÍSICA I</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
   </si>
 </sst>
 </file>
@@ -528,28 +531,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>31</v>
-      </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>46.67</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -563,28 +566,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>90.23999999999999</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1">
-        <v>9.76</v>
+        <v>65</v>
       </c>
       <c r="I3" s="2">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -598,28 +601,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>32.14</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -633,28 +636,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>81.58</v>
+        <v>42.86</v>
       </c>
       <c r="H5" s="1">
-        <v>18.42</v>
+        <v>57.14</v>
       </c>
       <c r="I5" s="2">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -668,25 +671,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>78.56999999999999</v>
+        <v>41.18</v>
       </c>
       <c r="H6" s="1">
-        <v>21.43</v>
+        <v>58.82</v>
       </c>
       <c r="I6" s="2">
         <v>6.1</v>
@@ -703,28 +706,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
-      </c>
       <c r="E7">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>57.89</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>42.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -735,31 +738,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -770,63 +773,63 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9">
         <v>31</v>
       </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
       <c r="F9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>93.33</v>
+        <v>81.58</v>
       </c>
       <c r="H9" s="1">
-        <v>6.67</v>
+        <v>18.42</v>
       </c>
       <c r="I9" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>28</v>
+      </c>
+      <c r="E10">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>14</v>
-      </c>
       <c r="F10">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>46.67</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>53.33</v>
+        <v>21.43</v>
       </c>
       <c r="I10" s="2">
         <v>6.1</v>
@@ -840,31 +843,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -875,66 +878,66 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
         <v>28</v>
       </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
       <c r="F12">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>32.14</v>
+        <v>93.33</v>
       </c>
       <c r="H12" s="1">
-        <v>67.86</v>
+        <v>6.67</v>
       </c>
       <c r="I12" s="2">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -945,31 +948,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>41.18</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>58.82</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -980,31 +983,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>57.89</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1015,13 +1018,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>34</v>
@@ -1050,13 +1053,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>24</v>
@@ -1085,13 +1088,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>14</v>
@@ -1175,19 +1178,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1196,7 +1199,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1207,19 +1210,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1228,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1239,19 +1242,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1260,7 +1263,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1271,19 +1274,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1292,7 +1295,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1303,19 +1306,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1324,7 +1327,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1335,19 +1338,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
-      </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1356,7 +1359,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1364,22 +1367,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1388,7 +1391,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1396,22 +1399,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1420,7 +1423,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1428,22 +1431,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1452,7 +1455,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1460,22 +1463,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1484,7 +1487,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1492,22 +1495,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1516,7 +1519,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1524,22 +1527,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1548,7 +1551,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1556,22 +1559,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1580,7 +1583,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1588,22 +1591,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1612,7 +1615,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1620,13 +1623,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>34</v>
@@ -1652,13 +1655,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>24</v>
@@ -1684,13 +1687,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>14</v>
@@ -1771,28 +1774,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>31</v>
-      </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>46.67</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>53.33</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1806,28 +1809,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>90.23999999999999</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1">
-        <v>9.76</v>
+        <v>65</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1841,28 +1844,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>32.14</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>67.86</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1876,28 +1879,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>81.58</v>
+        <v>42.86</v>
       </c>
       <c r="H5" s="1">
-        <v>18.42</v>
+        <v>57.14</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1911,28 +1914,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>78.56999999999999</v>
+        <v>41.18</v>
       </c>
       <c r="H6" s="1">
-        <v>21.43</v>
+        <v>58.82</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1946,28 +1949,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
-      </c>
       <c r="E7">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>57.89</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>42.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1978,31 +1981,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2013,66 +2016,66 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9">
         <v>31</v>
       </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
       <c r="F9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>93.33</v>
+        <v>81.58</v>
       </c>
       <c r="H9" s="1">
-        <v>6.67</v>
+        <v>18.42</v>
       </c>
       <c r="I9" s="2">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>28</v>
+      </c>
+      <c r="E10">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>14</v>
-      </c>
       <c r="F10">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>46.67</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>53.33</v>
+        <v>21.43</v>
       </c>
       <c r="I10" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2083,31 +2086,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2118,66 +2121,66 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
         <v>28</v>
       </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
       <c r="F12">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>32.14</v>
+        <v>93.33</v>
       </c>
       <c r="H12" s="1">
-        <v>67.86</v>
+        <v>6.67</v>
       </c>
       <c r="I12" s="2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2188,31 +2191,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>41.18</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>58.82</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2223,31 +2226,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>57.89</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2258,13 +2261,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>34</v>
@@ -2293,13 +2296,13 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>24</v>
@@ -2328,13 +2331,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>14</v>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="35">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -63,6 +62,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TEMAS DE FÍSICA</t>
+  </si>
+  <si>
+    <t>FÍSICA I</t>
+  </si>
+  <si>
     <t>6AEM</t>
   </si>
   <si>
@@ -112,12 +120,6 @@
   </si>
   <si>
     <t>4ASV</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
-  </si>
-  <si>
-    <t>FÍSICA I</t>
   </si>
 </sst>
 </file>
@@ -481,11 +483,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -531,10 +533,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -546,10 +548,10 @@
         <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>46.67</v>
+        <v>46.7</v>
       </c>
       <c r="H2" s="1">
-        <v>53.33</v>
+        <v>53.3</v>
       </c>
       <c r="I2" s="2">
         <v>6.1</v>
@@ -569,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -601,10 +603,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -616,10 +618,10 @@
         <v>19</v>
       </c>
       <c r="G4" s="1">
-        <v>32.14</v>
+        <v>32.1</v>
       </c>
       <c r="H4" s="1">
-        <v>67.86</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I4" s="2">
         <v>5.7</v>
@@ -636,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -651,10 +653,10 @@
         <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>42.86</v>
+        <v>42.9</v>
       </c>
       <c r="H5" s="1">
-        <v>57.14</v>
+        <v>57.1</v>
       </c>
       <c r="I5" s="2">
         <v>5.1</v>
@@ -671,10 +673,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -686,10 +688,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>41.18</v>
+        <v>41.2</v>
       </c>
       <c r="H6" s="1">
-        <v>58.82</v>
+        <v>58.8</v>
       </c>
       <c r="I6" s="2">
         <v>6.1</v>
@@ -706,10 +708,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -721,10 +723,10 @@
         <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>57.89</v>
+        <v>57.9</v>
       </c>
       <c r="H7" s="1">
-        <v>42.11</v>
+        <v>42.1</v>
       </c>
       <c r="I7" s="2">
         <v>5.9</v>
@@ -738,31 +740,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="G8" s="1">
-        <v>90.23999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="H8" s="1">
-        <v>9.76</v>
+        <v>57.8</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -776,28 +772,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>81.58</v>
+        <v>90.2</v>
       </c>
       <c r="H9" s="1">
-        <v>18.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -811,28 +807,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>78.56999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>21.43</v>
+        <v>18.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -846,28 +842,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="I11" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -881,104 +877,98 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>88.8</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -986,16 +976,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1018,66 +1008,66 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>58.82</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>41.18</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>54.17</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>45.83</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1088,37 +1078,194 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>99</v>
+      </c>
+      <c r="E18">
+        <v>99</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>34</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>14</v>
+      </c>
+      <c r="G19" s="1">
+        <v>58.8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
         <v>33</v>
       </c>
-      <c r="D18">
+      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1">
+        <v>54.2</v>
+      </c>
+      <c r="H20" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
         <v>12</v>
       </c>
-      <c r="F18">
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="G18" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H18" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="G21" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H21" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I21" s="2">
         <v>7.1</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22">
+        <v>72</v>
+      </c>
+      <c r="E22">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="H22" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>475</v>
+      </c>
+      <c r="E23">
+        <v>351</v>
+      </c>
+      <c r="F23">
+        <v>124</v>
+      </c>
+      <c r="G23" s="1">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>26.1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1128,11 +1275,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1178,31 +1325,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>53.3</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.3</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1213,28 +1363,31 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1242,31 +1395,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>67.90000000000001</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1274,31 +1430,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>57.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1306,31 +1465,34 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>17</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>58.8</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.3</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1338,63 +1500,63 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>19</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>42.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.2</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F8">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>42.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>57.8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1402,31 +1564,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1434,31 +1599,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>18.4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1466,31 +1634,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>21.4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.2</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1498,95 +1669,98 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>6.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.1</v>
       </c>
       <c r="J13">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>11.2</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.4</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1594,774 +1768,296 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.1</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D16">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.1</v>
       </c>
       <c r="J17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>99</v>
+      </c>
+      <c r="E18">
+        <v>99</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>34</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>14</v>
+      </c>
+      <c r="G19" s="1">
+        <v>58.8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
         <v>33</v>
       </c>
-      <c r="D18">
+      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1">
+        <v>54.2</v>
+      </c>
+      <c r="H20" s="1">
+        <v>45.8</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21">
         <v>14</v>
       </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
-      </c>
-      <c r="J18">
+      <c r="E21">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H21" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="D22">
+        <v>72</v>
+      </c>
+      <c r="E22">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>27</v>
+      </c>
+      <c r="G22" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="H22" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="J22">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="K22" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>475</v>
+      </c>
+      <c r="E23">
+        <v>351</v>
+      </c>
+      <c r="F23">
+        <v>124</v>
+      </c>
+      <c r="G23" s="1">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>26.1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="J23">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-      <c r="F2">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1">
-        <v>46.67</v>
-      </c>
-      <c r="H2" s="1">
-        <v>53.33</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1">
-        <v>35</v>
-      </c>
-      <c r="H3" s="1">
-        <v>65</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1">
-        <v>32.14</v>
-      </c>
-      <c r="H4" s="1">
-        <v>67.86</v>
-      </c>
-      <c r="I4" s="2">
-        <v>5.8</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5">
-        <v>21</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
-        <v>42.86</v>
-      </c>
-      <c r="H5" s="1">
-        <v>57.14</v>
-      </c>
-      <c r="I5" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>41.18</v>
-      </c>
-      <c r="H6" s="1">
-        <v>58.82</v>
-      </c>
-      <c r="I6" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7" s="1">
-        <v>57.89</v>
-      </c>
-      <c r="H7" s="1">
-        <v>42.11</v>
-      </c>
-      <c r="I7" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8">
-        <v>41</v>
-      </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="H8" s="1">
-        <v>9.76</v>
-      </c>
-      <c r="I8" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9">
-        <v>38</v>
-      </c>
-      <c r="E9">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="G9" s="1">
-        <v>81.58</v>
-      </c>
-      <c r="H9" s="1">
-        <v>18.42</v>
-      </c>
-      <c r="I9" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10">
-        <v>28</v>
-      </c>
-      <c r="E10">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10" s="1">
-        <v>78.56999999999999</v>
-      </c>
-      <c r="H10" s="1">
-        <v>21.43</v>
-      </c>
-      <c r="I10" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
-        <v>32</v>
-      </c>
-      <c r="E11">
-        <v>32</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12">
-        <v>30</v>
-      </c>
-      <c r="E12">
-        <v>28</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>93.33</v>
-      </c>
-      <c r="H12" s="1">
-        <v>6.67</v>
-      </c>
-      <c r="I12" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13">
-        <v>31</v>
-      </c>
-      <c r="E13">
-        <v>31</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14">
-        <v>27</v>
-      </c>
-      <c r="E14">
-        <v>27</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>100</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15">
-        <v>41</v>
-      </c>
-      <c r="E15">
-        <v>41</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>100</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16">
-        <v>34</v>
-      </c>
-      <c r="E16">
-        <v>20</v>
-      </c>
-      <c r="F16">
-        <v>14</v>
-      </c>
-      <c r="G16" s="1">
-        <v>58.82</v>
-      </c>
-      <c r="H16" s="1">
-        <v>41.18</v>
-      </c>
-      <c r="I16" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17">
-        <v>24</v>
-      </c>
-      <c r="E17">
-        <v>13</v>
-      </c>
-      <c r="F17">
-        <v>11</v>
-      </c>
-      <c r="G17" s="1">
-        <v>54.17</v>
-      </c>
-      <c r="H17" s="1">
-        <v>45.83</v>
-      </c>
-      <c r="I17" s="2">
-        <v>6</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18">
-        <v>14</v>
-      </c>
-      <c r="E18">
-        <v>12</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="H18" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="I18" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
+      <c r="K23" s="1">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
   <si>
     <t>Docente</t>
   </si>
@@ -62,13 +62,16 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>TEMAS DE FÍSICA</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>FÍSICA I</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>6AEM</t>
@@ -487,7 +490,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -533,10 +536,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -568,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -603,10 +606,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -638,10 +641,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -673,10 +676,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -708,10 +711,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -742,6 +745,9 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
       <c r="D8">
         <v>135</v>
       </c>
@@ -775,7 +781,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>41</v>
@@ -810,7 +816,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -845,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>28</v>
@@ -880,7 +886,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>32</v>
@@ -915,7 +921,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -946,6 +952,9 @@
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>169</v>
       </c>
@@ -979,7 +988,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>31</v>
@@ -1014,7 +1023,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>27</v>
@@ -1049,7 +1058,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>41</v>
@@ -1080,6 +1089,9 @@
       <c r="A18" t="s">
         <v>13</v>
       </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
       <c r="D18">
         <v>99</v>
       </c>
@@ -1113,7 +1125,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>34</v>
@@ -1148,7 +1160,7 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20">
         <v>24</v>
@@ -1183,7 +1195,7 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21">
         <v>14</v>
@@ -1214,6 +1226,9 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
       <c r="D22">
         <v>72</v>
       </c>
@@ -1240,8 +1255,8 @@
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="B23" t="s">
+        <v>18</v>
       </c>
       <c r="D23">
         <v>475</v>
@@ -1325,10 +1340,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -1360,10 +1375,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -1395,10 +1410,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>28</v>
@@ -1430,10 +1445,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -1465,10 +1480,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>17</v>
@@ -1500,10 +1515,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>19</v>
@@ -1534,6 +1549,9 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
       <c r="D8">
         <v>135</v>
       </c>
@@ -1567,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>41</v>
@@ -1602,7 +1620,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>38</v>
@@ -1637,7 +1655,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>28</v>
@@ -1672,7 +1690,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>32</v>
@@ -1707,7 +1725,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -1738,6 +1756,9 @@
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>169</v>
       </c>
@@ -1771,7 +1792,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>31</v>
@@ -1806,7 +1827,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>27</v>
@@ -1841,7 +1862,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>41</v>
@@ -1872,6 +1893,9 @@
       <c r="A18" t="s">
         <v>13</v>
       </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
       <c r="D18">
         <v>99</v>
       </c>
@@ -1905,7 +1929,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>34</v>
@@ -1940,7 +1964,7 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20">
         <v>24</v>
@@ -1975,7 +1999,7 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21">
         <v>14</v>
@@ -2006,6 +2030,9 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
       <c r="D22">
         <v>72</v>
       </c>
@@ -2032,8 +2059,8 @@
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="B23" t="s">
+        <v>18</v>
       </c>
       <c r="D23">
         <v>475</v>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="36">
   <si>
     <t>Docente</t>
   </si>
@@ -1349,6 +1350,810 @@
         <v>30</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>28</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>135</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>135</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>135</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>41</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>38</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>38</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>28</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>28</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>32</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>32</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>169</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>169</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>169</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>31</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>31</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>27</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>27</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17">
+        <v>41</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>41</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>41</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>99</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>99</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>99</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <v>34</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>34</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>34</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>24</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>24</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>14</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <v>72</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>72</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <v>475</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>475</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>475</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
       <c r="F2">

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -1132,25 +1132,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1">
-        <v>58.8</v>
+        <v>61.8</v>
       </c>
       <c r="H19" s="1">
-        <v>41.2</v>
+        <v>38.2</v>
       </c>
       <c r="I19" s="2">
         <v>5.9</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1234,25 +1234,25 @@
         <v>72</v>
       </c>
       <c r="E22">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
-        <v>62.5</v>
+        <v>63.9</v>
       </c>
       <c r="H22" s="1">
-        <v>37.5</v>
+        <v>36.1</v>
       </c>
       <c r="I22" s="2">
         <v>6.3</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1263,25 +1263,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F23">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G23" s="1">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="I23" s="2">
         <v>6.5</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1350,25 +1350,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>46.7</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1385,25 +1385,25 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1420,25 +1420,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>53.6</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>46.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1490,25 +1490,25 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1525,25 +1525,25 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1557,25 +1557,25 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F8">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1936,25 +1936,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J19">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1971,25 +1971,25 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J20">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2006,25 +2006,25 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J21">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2038,25 +2038,25 @@
         <v>72</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J22">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2067,25 +2067,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F23">
-        <v>475</v>
+        <v>376</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>79.2</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J23">
-        <v>475</v>
+        <v>268</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>56.4</v>
       </c>
     </row>
   </sheetData>
@@ -2154,19 +2154,19 @@
         <v>30</v>
       </c>
       <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>16</v>
-      </c>
       <c r="G2" s="1">
+        <v>53.3</v>
+      </c>
+      <c r="H2" s="1">
         <v>46.7</v>
       </c>
-      <c r="H2" s="1">
-        <v>53.3</v>
-      </c>
       <c r="I2" s="2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I3" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2224,19 +2224,19 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>32.1</v>
+        <v>53.6</v>
       </c>
       <c r="H4" s="1">
-        <v>67.90000000000001</v>
+        <v>46.4</v>
       </c>
       <c r="I4" s="2">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2259,19 +2259,19 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="H5" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="I5" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>41.2</v>
+        <v>35.3</v>
       </c>
       <c r="H6" s="1">
-        <v>58.8</v>
+        <v>64.7</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>42.1</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2361,19 +2361,19 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F8">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G8" s="1">
-        <v>42.2</v>
+        <v>47.4</v>
       </c>
       <c r="H8" s="1">
-        <v>57.8</v>
+        <v>52.6</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2740,25 +2740,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G19" s="1">
-        <v>58.8</v>
+        <v>32.4</v>
       </c>
       <c r="H19" s="1">
-        <v>41.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I19" s="2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2775,19 +2775,19 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="H20" s="1">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="I20" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>14.3</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>72</v>
       </c>
       <c r="E22">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F22">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1">
-        <v>62.5</v>
+        <v>48.6</v>
       </c>
       <c r="H22" s="1">
-        <v>37.5</v>
+        <v>51.4</v>
       </c>
       <c r="I22" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2871,25 +2871,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F23">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G23" s="1">
-        <v>73.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H23" s="1">
-        <v>26.1</v>
+        <v>26.7</v>
       </c>
       <c r="I23" s="2">
         <v>6.6</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -1592,25 +1592,25 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>87.8</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1627,25 +1627,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>18.4</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1662,25 +1662,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>60.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>39.3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1764,25 +1764,25 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F14">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>50.3</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2067,25 +2067,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="F23">
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="G23" s="1">
-        <v>20.8</v>
+        <v>38.5</v>
       </c>
       <c r="H23" s="1">
-        <v>79.2</v>
+        <v>61.5</v>
       </c>
       <c r="I23" s="2">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J23">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="K23" s="1">
-        <v>56.4</v>
+        <v>33.9</v>
       </c>
     </row>
   </sheetData>
@@ -2396,19 +2396,19 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>90.2</v>
+        <v>87.8</v>
       </c>
       <c r="H9" s="1">
-        <v>9.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>18.4</v>
       </c>
       <c r="I10" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2466,19 +2466,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>78.59999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="H11" s="1">
-        <v>21.4</v>
+        <v>39.3</v>
       </c>
       <c r="I11" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2568,19 +2568,19 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G14" s="1">
-        <v>88.8</v>
+        <v>85.2</v>
       </c>
       <c r="H14" s="1">
-        <v>11.2</v>
+        <v>14.8</v>
       </c>
       <c r="I14" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2871,19 +2871,19 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="F23">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G23" s="1">
-        <v>73.3</v>
+        <v>72</v>
       </c>
       <c r="H23" s="1">
-        <v>26.7</v>
+        <v>28</v>
       </c>
       <c r="I23" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J23">
         <v>1</v>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -928,25 +928,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="H13" s="1">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="I13" s="2">
         <v>6.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -960,25 +960,25 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1">
-        <v>88.8</v>
+        <v>89.3</v>
       </c>
       <c r="H14" s="1">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="I14" s="2">
         <v>6.3</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1263,25 +1263,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F23">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" s="1">
-        <v>74.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="H23" s="1">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="I23" s="2">
         <v>6.5</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1732,25 +1732,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1764,25 +1764,25 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="F14">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G14" s="1">
-        <v>49.7</v>
+        <v>61.5</v>
       </c>
       <c r="H14" s="1">
-        <v>50.3</v>
+        <v>38.5</v>
       </c>
       <c r="I14" s="2">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1">
-        <v>36.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2067,25 +2067,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F23">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="G23" s="1">
-        <v>38.5</v>
+        <v>42.7</v>
       </c>
       <c r="H23" s="1">
-        <v>61.5</v>
+        <v>57.3</v>
       </c>
       <c r="I23" s="2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J23">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="K23" s="1">
-        <v>33.9</v>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>
@@ -2536,25 +2536,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>93.3</v>
+        <v>66.7</v>
       </c>
       <c r="H13" s="1">
-        <v>6.7</v>
+        <v>33.3</v>
       </c>
       <c r="I13" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2568,25 +2568,25 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G14" s="1">
-        <v>85.2</v>
+        <v>80.5</v>
       </c>
       <c r="H14" s="1">
-        <v>14.8</v>
+        <v>19.5</v>
       </c>
       <c r="I14" s="2">
         <v>6.8</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2871,25 +2871,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F23">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G23" s="1">
-        <v>72</v>
+        <v>70.3</v>
       </c>
       <c r="H23" s="1">
-        <v>28</v>
+        <v>29.7</v>
       </c>
       <c r="I23" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -1697,25 +1697,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1764,25 +1764,25 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F14">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1">
-        <v>61.5</v>
+        <v>72.2</v>
       </c>
       <c r="H14" s="1">
-        <v>38.5</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>18.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1799,25 +1799,25 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1834,25 +1834,25 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1869,25 +1869,25 @@
         <v>41</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1901,25 +1901,25 @@
         <v>99</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F18">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2067,25 +2067,25 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="F23">
-        <v>272</v>
+        <v>155</v>
       </c>
       <c r="G23" s="1">
-        <v>42.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>57.3</v>
+        <v>32.6</v>
       </c>
       <c r="I23" s="2">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>27.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2501,19 +2501,19 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>56.2</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2568,16 +2568,16 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1">
-        <v>80.5</v>
+        <v>72.2</v>
       </c>
       <c r="H14" s="1">
-        <v>19.5</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="2">
         <v>6.8</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2871,16 +2871,16 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="F23">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G23" s="1">
-        <v>70.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>29.7</v>
+        <v>32.6</v>
       </c>
       <c r="I23" s="2">
         <v>6.8</v>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -1294,8 +1294,7 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1604,7 +1603,7 @@
         <v>12.2</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2098,8 +2097,7 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2154,19 +2152,19 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>53.3</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>46.7</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2189,19 +2187,19 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="H3" s="1">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2224,19 +2222,19 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>53.6</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>46.4</v>
+        <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2259,19 +2257,19 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>33.3</v>
+        <v>85.7</v>
       </c>
       <c r="H5" s="1">
-        <v>66.7</v>
+        <v>14.3</v>
       </c>
       <c r="I5" s="2">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2294,19 +2292,19 @@
         <v>17</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>35.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>64.7</v>
+        <v>17.6</v>
       </c>
       <c r="I6" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2329,16 +2327,16 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>57.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>42.1</v>
+        <v>31.6</v>
       </c>
       <c r="I7" s="2">
         <v>6.6</v>
@@ -2361,19 +2359,19 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F8">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1">
-        <v>47.4</v>
+        <v>85.2</v>
       </c>
       <c r="H8" s="1">
-        <v>52.6</v>
+        <v>14.8</v>
       </c>
       <c r="I8" s="2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2396,19 +2394,19 @@
         <v>41</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>12.2</v>
+        <v>4.9</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2466,19 +2464,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>60.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>39.3</v>
+        <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2501,19 +2499,19 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>56.2</v>
+        <v>93.8</v>
       </c>
       <c r="H12" s="1">
-        <v>43.8</v>
+        <v>6.2</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2536,19 +2534,19 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2568,19 +2566,19 @@
         <v>169</v>
       </c>
       <c r="E14">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="F14">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1">
-        <v>72.2</v>
+        <v>89.3</v>
       </c>
       <c r="H14" s="1">
-        <v>27.8</v>
+        <v>10.7</v>
       </c>
       <c r="I14" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2603,19 +2601,19 @@
         <v>31</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2638,19 +2636,19 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I16" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2673,19 +2671,19 @@
         <v>41</v>
       </c>
       <c r="E17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I17" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2705,19 +2703,19 @@
         <v>99</v>
       </c>
       <c r="E18">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I18" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2740,19 +2738,19 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1">
-        <v>32.4</v>
+        <v>58.8</v>
       </c>
       <c r="H19" s="1">
-        <v>67.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="I19" s="2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2775,16 +2773,16 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="H20" s="1">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="I20" s="2">
         <v>6.1</v>
@@ -2842,19 +2840,19 @@
         <v>72</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F22">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G22" s="1">
-        <v>48.6</v>
+        <v>62.5</v>
       </c>
       <c r="H22" s="1">
-        <v>51.4</v>
+        <v>37.5</v>
       </c>
       <c r="I22" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2871,19 +2869,19 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="F23">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="G23" s="1">
-        <v>67.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="H23" s="1">
-        <v>32.6</v>
+        <v>16</v>
       </c>
       <c r="I23" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J23">
         <v>0</v>

--- a/academias/Física - Estadisticos 20222.xlsx
+++ b/academias/Física - Estadisticos 20222.xlsx
@@ -2257,19 +2257,19 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>85.7</v>
+        <v>90.5</v>
       </c>
       <c r="H5" s="1">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1">
-        <v>85.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="I8" s="2">
         <v>6.8</v>
@@ -2869,16 +2869,16 @@
         <v>475</v>
       </c>
       <c r="E23">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F23">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" s="1">
-        <v>84</v>
+        <v>84.2</v>
       </c>
       <c r="H23" s="1">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="I23" s="2">
         <v>6.9</v>
